--- a/public/templates/customers_template.xlsx
+++ b/public/templates/customers_template.xlsx
@@ -399,11 +399,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E6"/>
   <cols>
-    <col min="1" max="1" width="20.83203125" customWidth="1"/>
-    <col min="2" max="2" width="30.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="20.83203125" customWidth="1"/>
-    <col min="5" max="5" width="40.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
+    <col min="2" max="2" width="20.83203125" customWidth="1"/>
+    <col min="3" max="3" width="25.83203125" customWidth="1"/>
+    <col min="4" max="4" width="18.83203125" customWidth="1"/>
+    <col min="5" max="5" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
